--- a/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Легенда" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ключевые операции'!$A$3:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ключевые операции'!$A$3:$P$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,11 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9ECEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +176,21 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -183,6 +203,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -193,6 +216,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -560,30 +586,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 03.09.2026 12:44</t>
+          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 03.09.2026 13:34</t>
         </is>
       </c>
     </row>
@@ -605,60 +632,65 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Время запуска (первое, частота, последнее)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Объект (обработка / регламент)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Источник замера</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Потоков сейчас</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Потоков макс</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Длительность сейчас, мин</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Длительность макс, мин</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Прогноз x10 линейный, мин</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Прогноз расчётный, мин</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Худший прогноз, ч</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Зависит от числа клиентов</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Предел, тыс. договоров</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Окно, мин</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -684,6 +716,7 @@
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -701,111 +734,123 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
+          <t>22:00, 1 раз, 22:00</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
           <t>внИсполнениеСделокТ+2_ДУ</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="9" t="n">
         <v>40.6</v>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>406</v>
-      </c>
       <c r="J5" s="9" t="n">
-        <v>176</v>
+        <v>69.8</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>756</v>
+        <v>40.6</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Нет (от сделок)</t>
+        </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>Масштабируется лучше линейной: расчётный прогноз вдвое ниже линейного x10 - работают пачки и 6 потоков. Потоки задаются настройкой, резерв ускорения есть.</t>
+          <t>от сделок</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>Прогноз x10 по договорам не применяется: длительность определяется числом сделок, а не договоров. Потоки задаются настройкой (сейчас 6).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Загрузка сделок за дату Т, открытие плановой позиции сделок Т по РДУ</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>12:30, 60 мин, 23:58</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>внЗагрузкаСделокDU-NEW</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="14" t="n">
+      <c r="G6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="I6" s="14" t="n">
-        <v>129</v>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="J6" s="9" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Нет (от сделок)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>от сделок</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>Узкое место - однопоточное получение из Tibco. Требуется многопоточный обмен.</t>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>Прогноз x10 по договорам не применяется: длительность определяется числом сделок. Получение из Tibco - 1 поток; создание сделок на ПРОД - 3 потока.</t>
         </is>
       </c>
     </row>
@@ -825,50 +870,55 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
+          <t>5:05, 1 раз, 5:05</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
           <t>внПакетныйОтчетБрокераДУ_ДВО</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="J7" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K7" s="9" t="n">
         <v>34.9</v>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Потоки зашиты в коде числом 6 - предел без доработки.</t>
         </is>
@@ -894,6 +944,7 @@
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -911,113 +962,123 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
+          <t>9:09, 1 раз, 9:09</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
           <t>внЗагрузкаВыписокДУ</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="14" t="n">
         <v>16.5</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="J9" s="14" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>165</v>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="N9" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="O9" s="10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Пул потоков настраивается реквизитом обработки, резерв ускорения есть. Многоэтапная операция: получение, разбор, создание документов.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Сверка денежных средств</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>14:30, 1 раз, 14:30</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>внСверкаДенежныхСредств_обр</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="G10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="H10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="19" t="n">
         <v>3.4</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="J10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="19" t="n">
         <v>33.9</v>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M10" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>Однопоточная агрегатная сверка. Уже сейчас 3,4 минуты при цели 6 минут - запас менее двукратного, при росте базы цель будет нарушена.</t>
+      <c r="N10" s="15" t="n">
+        <v>443</v>
+      </c>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>Однопоточная агрегатная сверка. При росте базы в 10 раз выходит за окно 60 минут.</t>
         </is>
       </c>
     </row>
@@ -1037,48 +1098,53 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
+          <t>17:00, 1 раз, 17:00</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
           <t>внСверкаДенежныхСредствНаЕРС_обр</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>0.06</v>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="J11" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="K11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - сверка идёт по 10 счетам ЕРС.</t>
         </is>
@@ -1100,50 +1166,55 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
+          <t>9:30, 5 мин, 23:55</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
           <t>внСинхронизацияНСИ (ФоновоеВыполнениеПоручения)</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="J12" s="9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K12" s="9" t="n">
         <v>0.78</v>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>ОЦЕНОЧНО: маппинг операции на внСинхронизацияНСИ требует подтверждения у постановщика. Замер снят по ключу поручений.</t>
         </is>
@@ -1169,6 +1240,7 @@
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1186,48 +1258,53 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
+          <t>9:00, 1 раз, 9:00</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
           <t>внЗагрузкаКотировокДУ</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>3.3</v>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>3.3</v>
       </c>
       <c r="J14" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="K14" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
@@ -1249,48 +1326,53 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
+          <t>9:15, 1 раз, 9:15</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
           <t>внОтчетКонтрольКотировок</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="9" t="n">
-        <v>0.1</v>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="J15" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="K15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
@@ -1312,48 +1394,53 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
+          <t>11:50, 1 раз, 11:50</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
           <t>внЗагрузкаКотировокДУ</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="9" t="n">
-        <v>2.7</v>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>2.7</v>
       </c>
       <c r="J16" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="K16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
@@ -1379,6 +1466,7 @@
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1396,174 +1484,197 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
+          <t>8:30, 1 раз, 8:30</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
           <t>внСверкаCделокДУСОтчетомБрокера</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="I18" s="14" t="n">
+      <c r="J18" s="14" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="K18" s="14" t="n">
         <v>147</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="L18" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="K18" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N18" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
+      <c r="N18" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="inlineStr">
         <is>
           <t>Однопоточная. Контур с проведением в 9 раз тяжелее контура без проведения.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Сверка остатков ЦБ с депозитарием</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>12:00, 1 раз, 12:00</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>внСверкаЦБ</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="G19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="H19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="I19" s="19" t="n">
         <v>3.8</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="J19" s="19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K19" s="19" t="n">
         <v>38.4</v>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="L19" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M19" s="10" t="n">
-        <v>195</v>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O19" s="13" t="inlineStr">
+      <c r="N19" s="15" t="n">
+        <v>391</v>
+      </c>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="inlineStr">
         <is>
           <t>Однопоточная, объём строк прямо пропорционален числу договоров.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Сверка API сигнал vs Реестры платежей</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>не реализовано (IMDEV-8274)</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="G20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="H20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>221</v>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O20" s="13" t="inlineStr">
-        <is>
-          <t>ОЦЕНОЧНО: операция не реализована (IMDEV-8274), замера нет. Цифра - аналогия со сверкой ДС, требует замера после реализации.</t>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>Замер в код не вставлен (операция не реализована, IMDEV-8274). Длительность и прогноз не рассчитываются - в таблице прочерк.</t>
         </is>
       </c>
     </row>
@@ -1587,6 +1698,7 @@
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1604,50 +1716,55 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
+          <t>7:00, 10 мин, 22:52</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
           <t>внРасторжениеДоговоровРозничногоДУ</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="J22" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K22" s="9" t="n">
         <v>0.18</v>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>Запускается каждые 10 минут, поток расторжений растёт пропорционально базе.</t>
         </is>
@@ -1669,48 +1786,53 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
+          <t>7:02, 10 мин, 23:52</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
           <t>внСинхронизацияНСИ (ФоновоеВыполнение)</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="n">
         <v>1.6</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="J23" s="14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K23" s="14" t="n">
         <v>15.5</v>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K23" s="14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="M23" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="N23" s="10" t="n">
         <v>161</v>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O23" s="13" t="inlineStr">
+      <c r="P23" s="13" t="inlineStr">
         <is>
           <t>Однопоточный обмен с 1С:ДО - аналог узкого места МО по загрузке статики.</t>
         </is>
@@ -1736,6 +1858,7 @@
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
@@ -1753,48 +1876,53 @@
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
+          <t>11:46, 1 раз, 11:46</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
           <t>Справочник.РегламентныеПериоды + Документ.ПланРегламентныхОперацийДУ</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Разработческая база</t>
         </is>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>12</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>42.4</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="J25" s="19" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K25" s="19" t="n">
         <v>424</v>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="L25" s="19" t="n">
         <v>297</v>
       </c>
-      <c r="K25" s="19" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="M25" s="17" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M25" s="15" t="n">
+      <c r="N25" s="15" t="n">
         <v>413</v>
       </c>
-      <c r="N25" s="15" t="inlineStr">
+      <c r="O25" s="15" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>Замер с разработческой базы (оптимизация, скоро на ПРОД). На ПРОД сейчас та же операция идёт около 118 минут.</t>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
+          <t>Длительность - с разработческой базы (оптимизация, скоро на ПРОД); на ПРОД сейчас та же операция идёт около 118 минут. Время запуска - по замерам ПРОД на полном объёме.</t>
         </is>
       </c>
     </row>
@@ -1814,46 +1942,51 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
+          <t>14:23, 1 раз, 14:23</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
           <t>Справочник.РегламентныеПериоды + Документ.ПланРегламентныхОперацийДУ</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>12</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="14" t="n">
         <v>60.1</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="J26" s="14" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="K26" s="14" t="n">
         <v>601</v>
       </c>
-      <c r="J26" s="14" t="n">
+      <c r="L26" s="14" t="n">
         <v>667</v>
       </c>
-      <c r="K26" s="14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="M26" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="N26" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O26" s="13" t="inlineStr">
+      <c r="P26" s="13" t="inlineStr">
         <is>
           <t>На полном объёме базы зафиксирован один прогон - точность оценки ограничена.</t>
         </is>
@@ -1879,6 +2012,7 @@
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -1896,109 +2030,131 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
+          <t>-, 1 раз/квартал, -</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
           <t>внНачислениеВознаграждения_РозничноеДУ</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>12</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="14" t="n">
         <v>63.5</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="n">
         <v>635</v>
       </c>
-      <c r="J28" s="14" t="n">
+      <c r="L28" s="14" t="n">
         <v>635</v>
       </c>
-      <c r="K28" s="14" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="M28" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="N28" s="10" t="n">
         <v>189</v>
       </c>
-      <c r="N28" s="10" t="inlineStr">
+      <c r="O28" s="10" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O28" s="13" t="inlineStr">
+      <c r="P28" s="13" t="inlineStr">
         <is>
           <t>ОЦЕНОЧНО: массового квартального прогона в выгрузке нет, есть только единичные договоры. Длительность пересчитана от удельной стоимости одного договора на всю базу с учётом 12 потоков. Требуется замер квартального прогона.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>Оплата вознаграждения</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Ежеквартально</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>внОплатаКЗПоКлиентамРДУ (замер не реализован)</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="G29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="H29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>762</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>7621</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>7621</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>нет замеров</t>
+        </is>
+      </c>
+      <c r="M29" s="22" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M29" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O29" s="13" t="inlineStr">
-        <is>
-          <t>ОЦЕНОЧНО, ВЕРХНЯЯ ГРАНИЦА: в коде внОплатаКЗПоКлиентамРДУ замера нет вообще - его надо добавить. Расчёт исходит из того, что оплата идёт по всем договорам последовательно в один поток. Фактически обрабатываются только договоры с задолженностью, поэтому реальная длительность будет ниже.</t>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>Замер в код внОплатаКЗПоКлиентамРДУ не вставлен. Длительность и прогноз не рассчитываются - в таблице прочерк. Нужно добавить замер в обработку.</t>
         </is>
       </c>
     </row>
@@ -2018,46 +2174,53 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
+          <t>17:00, 1 раз, 17:00</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
           <t>внОтчетУправляющегоДУсогласно482П_v15 + внЗапускПоРасписаниюОтчетаУправляющегоДУ</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>10</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="14" t="n">
         <v>565</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="n">
         <v>5652</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="L30" s="14" t="n">
         <v>5652</v>
       </c>
-      <c r="K30" s="14" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="M30" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="N30" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="N30" s="10" t="inlineStr">
+      <c r="O30" s="10" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O30" s="13" t="inlineStr">
+      <c r="P30" s="13" t="inlineStr">
         <is>
           <t>ОЦЕНОЧНО, НИЖНЯЯ ГРАНИЦА: показано время на ВСЕ договоры РДУ. Один замер в регистре - это один отчёт по одному договору (в ДопИнф стоит конкретный ДоговорДУ, вес = 1), таких замеров 966. Квартальный прогон обходит весь пул "Розничное ДУ", то есть строит по отчёту на договор. Расчёт: 25 тыс. отчётов по 13,6 с при 10 потоках. Это нижняя граница: при конкуренции за ресурсы время одного отчёта вырастет. Замер массового прогона в коде УЖЕ ЕСТЬ (ключ "Отчет Управляющего ДУ 482П РозничноеДУ выгрузка", вес = число договоров), но в выгрузке его нет - в окно 28.07-02.09 квартальный прогон не попал. Нужна выгрузка за начало квартала, а не доработка кода.</t>
         </is>
@@ -2083,6 +2246,7 @@
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2100,48 +2264,53 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
+          <t>10:00, 10 мин, 23:52</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
           <t>внЭкспортДанныхКабиентHNWI_DU</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="J32" s="9" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>0.96</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="L32" s="9" t="n">
         <v>0.22</v>
       </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="P32" s="8" t="inlineStr">
         <is>
           <t>Аналог узкого места МО (выгрузка в кабинет клиента). Здесь работает инкрементально каждые 10 минут, поэтому длительность одного прогона мала, но есть прогоны до 79 минут.</t>
         </is>
@@ -2163,48 +2332,53 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
+          <t>15:00, 1 раз, 15:00</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
           <t>внРаспределениеДоходовПоЦеннымБумагам</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>12</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="J33" s="9" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K33" s="9" t="n">
         <v>157</v>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="N33" s="5" t="n">
         <v>765</v>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="P33" s="8" t="inlineStr">
         <is>
           <t>В выгрузке всего один замер - статистика недостаточна.</t>
         </is>
@@ -2226,50 +2400,55 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
+          <t>8:00, 1 раз, 8:00</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
           <t>внРасчетВознагражденияРозничногоДУ</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="9" t="n">
         <v>0.19</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="J34" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="P34" s="8" t="inlineStr">
         <is>
           <t>В наблюдаемом периоде ДоговоровКРасчету = 0, то есть замерено холостое прохождение. Нагрузочная оценка требует прогона в квартальную дату.</t>
         </is>
@@ -2291,65 +2470,70 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
+          <t>10:53, 1 раз, 10:53</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
           <t>внОтрицательныеОстаткиНаАналитическомСчете</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9" t="n">
         <v>0.01</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>0.05</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
+        <v>0.05</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="P35" s="8" t="inlineStr">
         <is>
           <t>Ручной отчёт, работает быстро.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O35"/>
+  <autoFilter ref="A3:P35"/>
   <mergeCells count="9">
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A8:P8"/>
+    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A21:P21"/>
+    <mergeCell ref="A24:P24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2376,288 +2560,288 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Исполнение сделок (авто закрытие Т-1, Т-2)</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Порции нарезаются по ДоговорДУ, объём работы - сделки по этим договорам. Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Ночное окно 22:00-06:00. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Слабо зависит от числа договоров. Объём работы - число сделок за день (порции нарезаются по ДоговорДУ, но длительность задают сделки). Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Загрузка сделок за дату Т, открытие плановой позиции сделок Т по РДУ</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Объём - число сделок за день, растёт пропорционально клиентской базе. Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок умеет параллелиться по пачкам договоров, но по умолчанию КоличествоПотоков=1. Окно: Сеанс идёт несколько раз в день, окно между сеансами. Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Слабо зависит от числа договоров. Объём - число сделок за день. Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Сеанс идёт несколько раз в день, окно между сеансами. Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Обработка отчётов брокера за Т-1</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 1014 строк отчёта. Зависимость от базы: Объём - строки отчёта брокера (СтрокSQL), растут с числом договоров. Потоки: КоличествоПотоков = 6 задано жёстко в коде; ограничение "один договор - один поток" не позволяет поднять без переработки. Окно: Старт 05:05, до начала операционного дня 09:00. Ключевые операции регистра: Д у. пакетный отчет брокера. получение s q l. фоновое выполнение; Д у. пакетный отчет брокера. создание операций. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Загрузка выписок банка</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 26 дням. Замеров в выгрузке: 26. Типовой объём замера: 2 платежей. Зависимость от базы: Группы нарезаются по паре (БанковскийСчет, ДоговорДУ); объём - выписки и платежи. Потоки: Реквизит МаксПараллельныхГрупп, по умолчанию 3. Резерв по потокам: Предел - число групп (БанковскийСчет, ДоговорДУ), с ростом базы он только растёт. Пул можно поднять настройкой без доработки кода. Окно: Операционное утро, до 10:00. Ключевые операции регистра: Д у. загрузка выписок. получение w e b_ v t b. заполнить w e b_ v t b; Д у. загрузка выписок. разбор выписок. заполнить w e b_ v t b; Д у. загрузка выписок. создание документов. разобрать отмеченные.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Сверка денежных средств</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 расхождений. Зависимость от базы: Строки результата - комбинации ДоговорДУ + Счёт + Валюта из базы. Потоки: Один SQL-запрос с группировкой, распараллеливание не предусмотрено. Окно: Цель IMDEV-8927: не дольше 6 минут. Ключевые операции регистра: Д у. сверка денежных средств. сверка. фоновое выполнение.</t>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 расхождений. Зависимость от базы: Строки результата - комбинации ДоговорДУ + Счёт + Валюта из базы. Потоки: Один SQL-запрос с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Сверка денежных средств ЕРС</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 счетов с расхождением. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 2 счетов с расхождением -&gt; 2 с (n=2) и 3 счетов с расхождением -&gt; 9 с (n=3), то есть 6.6030 с на единицу плюс постоянные 0 с. Зависимость от базы: Сверяются итоги по 10 жёстко заданным счётам ЕРС, а не каждый договор. Число счетов от клиентской базы не зависит. Потоки: Цикл по фиксированному списку 10 счетов ЕРС. Окно: Цель IMDEV-8927: не дольше 6 минут. Ключевые операции регистра: Д у. сверка денежных средств е р с. сверка. фоновое выполнение.</t>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 счетов с расхождением. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 2 счетов с расхождением -&gt; 2 с (n=2) и 3 счетов с расхождением -&gt; 9 с (n=3), то есть 6.6030 с на единицу плюс постоянные 0 с. Зависимость от базы: Сверяются итоги по 10 жёстко заданным счётам ЕРС, а не каждый договор. Число счетов от клиентской базы не зависит. Потоки: Цикл по фиксированному списку 10 счетов ЕРС. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств е р с. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Перевод денежных средств на биржу (формирование п/п) датой Т</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 6119 замерам. Замеров в выгрузке: 6119. Типовой объём замера: 1 поручений. Зависимость от базы: Вес замера - число поручений, растёт с числом договоров. Потоки: Последовательная синхронизация с 1С:ДО, пула потоков нет. Окно: Запуск каждые 5-10 минут. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение поручения.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Загрузка котировок 1-й сеанс за дату Т-1</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов (около 3 600 котировок), от числа договоров РДУ не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Сверка загрузки котировок</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 302 строк отчёта. Зависимость от базы: Строки отчёта - инструменты (Актив x Биржа), около 300 строк. Потоки: Один запрос, распараллеливание не предусмотрено. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. контроль котировок. отчет. фоновое выполнение.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 302 строк отчёта. Зависимость от базы: Строки отчёта - инструменты (Актив x Биржа), около 300 строк. Потоки: Один запрос, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. контроль котировок. отчет. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Загрузка котировок финальная за Т-1</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов, от числа договоров не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Сверка с отчётом брокера</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 35 замерам. Замеров в выгрузке: 35. Типовой объём замера: 7989 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1087 сделок -&gt; 163 с (n=7) и 8536 сделок -&gt; 997 с (n=26), то есть 0.1120 с на единицу плюс постоянные 41 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Старт 08:45, до начала операционного дня 09:15. Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое проведение.</t>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 35 замерам. Замеров в выгрузке: 35. Типовой объём замера: 7989 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1087 сделок -&gt; 163 с (n=7) и 8536 сделок -&gt; 997 с (n=26), то есть 0.1120 с на единицу плюс постоянные 41 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Окно сверки не менее 60 минут (старт 08:45). Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое проведение.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Сверка остатков ЦБ с депозитарием</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 строк сверки. Зависимость от базы: Строки сверки - ДоговорДУ x ЦБ, сейчас около 121 000 строк. Потоки: Один SQL с группировкой, распараллеливание не предусмотрено. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. сверка ц б. сверка. фоновое выполнение.</t>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 строк сверки. Зависимость от базы: Строки сверки - ДоговорДУ x ЦБ, сейчас около 121 000 строк. Потоки: Один SQL с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка ц б. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Сверка API сигнал vs Реестры платежей</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: оценка по аналогии с операцией "Сверка денежных средств". Типовой объём замера: 1 платежей. Зависимость от базы: По смыслу зависит от числа платежей, то есть от клиентской базы. Потоки: Операция не реализована, замера нет. Окно: Принято по аналогии с прочими сверками. Оценка по аналогии со сверкой денежных средств (тот же класс: один агрегатный запрос по платежам и счетам договоров, один поток).</t>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: замер в код не вставлен. Зависимость от базы: По смыслу зависит от числа платежей, то есть от клиентской базы. Потоки: Операция не реализована, замера в коде нет. Окно: Окно сверки не менее 60 минут.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Процесс расторжения РДУ</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 3398 замерам. Замеров в выгрузке: 3398. Типовой объём замера: 137 договоров. Зависимость от базы: Вес замера - число договоров к расторжению из 1С:ДО. Потоки: Последовательная обработка договоров, пула потоков нет. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. расторжение договоров р д у. фоновое договоры из д о к расторжению.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Загрузка договоров РДУ за дату Т, карточки клиента, автозаполнение аналитики для ВУ</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 3607 замерам. Замеров в выгрузке: 3607. Типовой объём замера: 1 объектов НСИ. Зависимость от базы: Объём - новые объекты НСИ (договоры, карточки), поток растёт с базой. Потоки: Последовательный обмен с 1С:ДО, распараллеливание не предусмотрено. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Вечерние регламентные операции, расчёт РСА/СЧА за Т-1</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 3 замерам. Замеров в выгрузке: 3. Типовой объём замера: 21994 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3087 договоров -&gt; 1274 с (n=4) и 21994 договоров -&gt; 2542 с (n=3), то есть 0.0671 с на единицу плюс постоянные 1067 с. Зависимость от базы: Прямой перебор договоров РДУ: пачки по 3 000, чанки по 50 договоров на поток. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999, жёсткого предела в коде нет - резерв ограничен только ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. регламентные операции.2. вечерние операции.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Утренние регламентные операции, начисления % по депозитам, РЕПО, НКД, погашения за дату Т</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 22889 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3090 договоров -&gt; 437 с (n=27) и 22889 договоров -&gt; 3606 с (n=1), то есть 0.1601 с на единицу плюс постоянные 0 с. Зависимость от базы: Прямой перебор договоров РДУ, тот же диспетчер пачек, что у вечерних. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999 - резерв ограничен ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. регламентные операции.1. утренние операции.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Начисление вознаграждения</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Длительность: пересчёт от удельной стоимости договора. Замеров в выгрузке: 253. Типовой объём замера: 1 договоров. Модель роста: удельная стоимость одного договора 1.83 с, при 12 потоках это 0.152 с на договор; развёрнуто на всю базу. Зависимость от базы: Вес замера - число договоров к начислению. Потоки: Пул фоновых заданий, лимит из константы (12), пачки по 100 договоров зашиты в коде. Резерв по потокам: Лимит берётся из той же константы, что у регламентов - резерв ограничен ресурсами кластера. Окно: Квартальное закрытие, ночное окно. Ключевые операции регистра: Д у. начисление вознаграждения р д у. начисление. ручной; Д у. начисление вознаграждения р д у. начисление. начисление вознаграждения при расторжении розничное д у фоновое.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Оплата вознаграждения</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>Длительность: пересчёт от удельной стоимости договора операции "Начисление вознаграждения". Модель роста: удельная стоимость одного договора 1.83 с, при 1 потоках это 1.829 с на договор; развёрнуто на всю базу. Зависимость от базы: Отбор договоров РДУ, объём прямо пропорционален базе. Потоки: Последовательный перебор строк ДокументыКВыгрузке, пула потоков нет. Окно: Квартальное закрытие, ночное окно. Удельная стоимость договора взята у начисления вознаграждения (соседний этап того же квартального процесса по тому же списку договоров), пересчёт - на 1 поток.</t>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: замер в код не вставлен. Зависимость от базы: Отбор договоров РДУ, объём прямо пропорционален базе. Потоки: Последовательный перебор строк ДокументыКВыгрузке, пула потоков нет. Окно: Квартальное закрытие, ночное окно.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Длительность: пересчёт от удельной стоимости договора. Замеров в выгрузке: 552. Типовой объём замера: 1 договоров. Модель роста: удельная стоимость одного договора 13.56 с, при 10 потоках это 1.357 с на договор; развёрнуто на всю базу. Зависимость от базы: Регламент обрабатывает очередь регистра СостоянияВыгрузкиОтчетовДУ. Очередь пополняется, когда пуста: квартально - всем пулом "Розничное ДУ", плюс ежедневно договорами с датой окончания. То есть квартальный прогон - это один отчёт на каждый договор РДУ. Потоки: Реквизит Отчет.КоличествоПотоков. В обработчиках формы стоит жёсткая отсечка: если больше 10, значение сбрасывается в 10. Многопоточность работает только в режиме "по клиентам розничного ДУ в фоновых потоках" (РежимРаботы=2) - именно он используется регламентом. Окно: Ночное окно 8 часов после старта 17:00. Ключевые операции регистра: Отчет управляющего д у 482 п.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Выгрузка данных в кабинет клиента ДУ (экспорт HNWI)</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 2944 замерам. Замеров в выгрузке: 2944. Типовой объём замера: 1 клиентов и дат. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3 клиентов и дат -&gt; 8 с (n=149) и 5 клиентов и дат -&gt; 10 с (n=386), то есть 0.7648 с на единицу плюс постоянные 6 с. Зависимость от базы: Вес замера - клиенты и даты инвестирования. Потоки: Последовательная выгрузка, ограничение на стороне принимающей системы (кабинет). Окно: Инкрементальный запуск каждые 10 минут. Ключевые операции регистра: Д у. экспорт h n w i. выгрузка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Распределение доходов по ценным бумагам</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 13361 строк НКД. Зависимость от базы: Объём - отмеченные строки НКД/погашений/дивидендов по позициям договоров. Потоки: Лимит из константы МаксимальноеКоличествоПараллельныхПотоков (12), пачки по 100 строк. Резерв по потокам: Резерв ограничен ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. распределение доходов. создание операций.вн распределение доходов по ценным бумагам.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Расчёт вознаграждения РДУ (ожидаемые платежи)</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 договоров к расчёту. Зависимость от базы: Отбор договоров пула Розничное ДУ. Потоки: Последовательный перебор ДоговорыДУКРасчету. Окно: Старт 08:00, до начала операционного дня. Ключевые операции регистра: Д у. расчет вознаграждения р д у. расчет. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Отчёт по отрицательным остаткам на РС</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 9 замерам. Замеров в выгрузке: 9. Типовой объём замера: 1 строк с минусом. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1 строк с минусом -&gt; 0 с (n=8) и 38 строк с минусом -&gt; 1 с (n=1), то есть 0.0077 с на единицу плюс постоянные 0 с. Зависимость от базы: Группировка АналитическийСчет + ДоговорДУ + Валюта по пулу Розничное ДУ. Потоки: Один запрос ОСВ, распараллеливание не предусмотрено. Окно: Принято по аналогии с прочими сверками. Ключевые операции регистра: Д у. сверка. отрицательные остатки на р с. формирование отчета. ручной.</t>
         </is>
@@ -2674,7 +2858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2682,142 +2866,178 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Подсветка строки</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr"/>
+      <c r="B1" s="26" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Красный</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Предел ниже целевых 250 тыс. договоров - операция не выдержит рост базы.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Жёлтый</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Предел от 250 до 500 тыс. договоров - запас менее двукратного.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Зелёный</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Запас достаточный либо операция не зависит от числа клиентов.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr"/>
-      <c r="B5" s="21" t="inlineStr"/>
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Серый</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Замер в код не вставлен: длительность и прогноз не рассчитываются (прочерк).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr"/>
+      <c r="B6" s="26" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Длительность сейчас</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Медиана прогонов на полном объёме базы: только регламентный контур, вес замера от 15 тыс. договоров, аварийные замеры исключены.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Длительность макс</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Максимум длительности среди тех же отобранных замеров (полный объём, без аварийных).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Время запуска</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>По фактическим замерам: первое типичное время старта за день, частота запусков, последнее типичное время старта. Формат: ЧЧ:ММ, N мин (или 1 раз), ЧЧ:ММ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Прогноз x10 линейный</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Текущая длительность, умноженная на 10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Текущая длительность, умноженная на 10. Не применяется к операциям, не зависящим от числа договоров (котировки, счета ЕРС, загрузка/исполнение сделок).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Прогноз расчётный</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>Линейная модель ПостояннаяЧасть + СтоимостьДоговора * ЧислоДоговоров. Наклон по двум самым крупным уровням объёма из фактических замеров.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Худший прогноз</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Максимум из двух оценок прогноза, в часах.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Линейная модель ПостояннаяЧасть + СтоимостьЕдиницы * Объём. Наклон по двум самым крупным уровням объёма из фактических замеров.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Потоков макс</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Только предел, подтверждённый кодом: жёсткое значение, ограничение интерфейса или значение константы. Где предел упирается в ресурсы кластера, а не в код, максимум приравнен к текущему значению, а резерв описан на листе "Методика и детали".</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Предел, тыс. договоров</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Число договоров, при котором операция упирается в своё окно выполнения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Число договоров, при котором операция упирается в своё окно выполнения. Для загрузки/исполнения сделок - "от сделок" (окно исполнения: 2 ч на 200 тыс. сделок).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Пометка "оценка"</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Массового прогона в выгрузке нет, цифра получена пересчётом от удельной стоимости договора или по аналогии. Требуется замер.</t>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Массового прогона в выгрузке нет, цифра получена пересчётом от удельной стоимости договора. Требуется замер массового прогона.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Пометка "нет замеров"</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Замер в код не вставлен. Расчёт по аналогии не делается - в ячейках прочерк.</t>
         </is>
       </c>
     </row>

--- a/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Легенда" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ключевые операции'!$A$3:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ключевые операции'!$A$3:$P$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -78,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF7EE"/>
+        <fgColor rgb="00FDECEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
+        <fgColor rgb="00EAF7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,6 +94,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E9ECEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,6 +196,21 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -206,16 +226,22 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -586,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -610,7 +636,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 03.09.2026 13:34</t>
+          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 03.09.2026 14:47</t>
         </is>
       </c>
     </row>
@@ -760,20 +786,18 @@
         <v>69.8</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>40.6</v>
+        <v>406</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>40.6</v>
+        <v>176</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Нет (от сделок)</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>от сделок</t>
-        </is>
+          <t>Да (через сделки)</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>158</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -782,7 +806,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>Прогноз x10 по договорам не применяется: длительность определяется числом сделок, а не договоров. Потоки задаются настройкой (сейчас 6).</t>
+          <t>Прогноз x10 применён по допущению: сделок на договор не меняется, база x10 -&gt; сделки x10. Потоков сейчас 6. При ~196 тыс. сделок/день на 250 тыс. договоров упирается и в окно 2 ч, и в лимит 200 тыс. сделок.</t>
         </is>
       </c>
     </row>
@@ -828,20 +852,20 @@
         <v>29.3</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>12.9</v>
+        <v>129</v>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>Нет (от сделок)</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>от сделок</t>
-        </is>
+          <t>Да (через сделки)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -850,75 +874,75 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>Прогноз x10 по договорам не применяется: длительность определяется числом сделок. Получение из Tibco - 1 поток; создание сделок на ПРОД - 3 потока.</t>
+          <t>Прогноз x10 применён по допущению постоянной интенсивности сделок на договор. Получение из Tibco - 1 поток; создание на ПРОД - 3 потока.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Обработка отчётов брокера за Т-1</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>5:05, 1 раз, 5:05</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>внПакетныйОтчетБрокераДУ_ДВО</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="14" t="n">
         <v>15.1</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="14" t="n">
         <v>34.9</v>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>Потоки зашиты в коде числом 6 - предел без доработки.</t>
         </is>
@@ -947,68 +971,68 @@
       <c r="P8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Загрузка выписок банка</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>9:09, 1 раз, 9:09</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>внЗагрузкаВыписокДУ</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="9" t="n">
         <v>73.3</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="9" t="n">
         <v>165</v>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="O9" s="10" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="P9" s="8" t="inlineStr">
         <is>
           <t>Пул потоков настраивается реквизитом обработки, резерв ускорения есть. Многоэтапная операция: получение, разбор, создание документов.</t>
         </is>
@@ -1083,138 +1107,138 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Сверка денежных средств ЕРС</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>17:00, 1 раз, 17:00</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>внСверкаДенежныхСредствНаЕРС_обр</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P11" s="8" t="inlineStr">
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - сверка идёт по 10 счетам ЕРС.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Перевод денежных средств на биржу (формирование п/п) датой Т</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>9:30, 5 мин, 23:55</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>внСинхронизацияНСИ (ФоновоеВыполнениеПоручения)</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="14" t="n">
         <v>0.08</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="14" t="n">
         <v>0.34</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="14" t="n">
         <v>0.78</v>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="O12" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t>ОЦЕНОЧНО: маппинг операции на внСинхронизацияНСИ требует подтверждения у постановщика. Замер снят по ключу поручений.</t>
         </is>
@@ -1243,204 +1267,204 @@
       <c r="P13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Загрузка котировок 1-й сеанс за дату Т-1</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>9:00, 1 раз, 9:00</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>внЗагрузкаКотировокДУ</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="14" t="n">
         <v>3.3</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="14" t="n">
         <v>3.3</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="14" t="n">
         <v>3.3</v>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Сверка загрузки котировок</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>9:15, 1 раз, 9:15</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>внОтчетКонтрольКотировок</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="14" t="n">
         <v>0.33</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="P15" s="13" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Загрузка котировок финальная за Т-1</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>11:50, 1 раз, 11:50</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>внЗагрузкаКотировокДУ</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="14" t="n">
         <v>2.7</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="14" t="n">
         <v>3.3</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="14" t="n">
         <v>2.7</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="14" t="n">
         <v>2.7</v>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>не зависит</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="P16" s="13" t="inlineStr">
         <is>
           <t>Не зависит от количества договоров - объём задают инструменты.</t>
         </is>
@@ -1484,7 +1508,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>8:30, 1 раз, 8:30</t>
+          <t>9:00, 60 мин, 12:00</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1504,24 +1528,24 @@
         <v>1</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>14.7</v>
+        <v>1.7</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>46.5</v>
+        <v>5.8</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>147</v>
+        <v>16.8</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>150</v>
+        <v>26.9</v>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Да (через сделки)</t>
         </is>
       </c>
       <c r="N18" s="10" t="n">
-        <v>99</v>
+        <v>558</v>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
@@ -1530,7 +1554,7 @@
       </c>
       <c r="P18" s="13" t="inlineStr">
         <is>
-          <t>Однопоточная. Контур с проведением в 9 раз тяжелее контура без проведения.</t>
+          <t>Однопоточная. В расчёт берётся только контур без проведения ("фоновое выполнение", РДУ). Контур с проведением ("фоновое проведение") - для сделок НЕ РДУ, в расчётах не учитывается (он примерно в 9 раз тяжелее и к Розничному ДУ не относится).</t>
         </is>
       </c>
     </row>
@@ -1603,78 +1627,71 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Сверка API сигнал vs Реестры платежей</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Сверка API сигнал vs Реестры платежей
+реальное название: Отчёт по отрицательным остаткам на р/с</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>не реализовано (IMDEV-8274)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>10:53, 1 раз, 10:53</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>внОтрицательныеОстаткиНаАналитическомСчете (IMDEV-8274)</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="I20" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>&gt; 1 000</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>Замер в код не вставлен (операция не реализована, IMDEV-8274). Длительность и прогноз не рассчитываются - в таблице прочерк.</t>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>Реальное название: Отчёт по отрицательным остаткам на р/с (внОтрицательныеОстаткиНаАналитическомСчете). В списке технического архитектора указано как "Сверка API сигнал vs Реестры платежей" (уточнено в IMDEV-9336 / IMDEV-8274). Замеры есть.</t>
         </is>
       </c>
     </row>
@@ -1701,140 +1718,138 @@
       <c r="P21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Процесс расторжения РДУ</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>7:00, 10 мин, 22:52</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>внРасторжениеДоговоровРозничногоДУ</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="14" t="n">
         <v>0.02</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O22" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="P22" s="13" t="inlineStr">
         <is>
           <t>Запускается каждые 10 минут, поток расторжений растёт пропорционально базе.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Загрузка договоров РДУ за дату Т, карточки клиента, автозаполнение аналитики для ВУ</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>7:02, 10 мин, 23:52</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>внСинхронизацияНСИ (ФоновоеВыполнение)</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I23" s="19" t="n">
         <v>1.6</v>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="J23" s="19" t="n">
         <v>7.3</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="19" t="n">
         <v>15.5</v>
       </c>
-      <c r="L23" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="L23" s="19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P23" s="13" t="inlineStr">
-        <is>
-          <t>Однопоточный обмен с 1С:ДО - аналог узкого места МО по загрузке статики.</t>
+      <c r="N23" s="15" t="n">
+        <v>483</v>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t>Однопоточный обмен с 1С:ДО. В расчёт берётся средний вес замера (новые объекты за запуск), прогноз x10 = длительность при среднем весе, умноженном на 10. Не путать с полным объёмом базы договоров.</t>
         </is>
       </c>
     </row>
@@ -1861,134 +1876,134 @@
       <c r="P24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Вечерние регламентные операции, расчёт РСА/СЧА за Т-1</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>11:46, 1 раз, 11:46</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Справочник.РегламентныеПериоды + Документ.ПланРегламентныхОперацийДУ</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Разработческая база</t>
         </is>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="I25" s="9" t="n">
         <v>42.4</v>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="J25" s="9" t="n">
         <v>44.9</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="9" t="n">
         <v>424</v>
       </c>
-      <c r="L25" s="19" t="n">
+      <c r="L25" s="9" t="n">
         <v>297</v>
       </c>
-      <c r="M25" s="17" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N25" s="15" t="n">
-        <v>413</v>
-      </c>
-      <c r="O25" s="15" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P25" s="18" t="inlineStr">
-        <is>
-          <t>Длительность - с разработческой базы (оптимизация, скоро на ПРОД); на ПРОД сейчас та же операция идёт около 118 минут. Время запуска - по замерам ПРОД на полном объёме.</t>
+      <c r="N25" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>Длительность - с разработческой базы после оптимизации IMDEV-8863.1 (фоновые); на ПРОД до выкладки та же операция шла около 118 минут (ускорение примерно в 2 раза). Время запуска - по замерам ПРОД.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Утренние регламентные операции, начисления % по депозитам, РЕПО, НКД, погашения за дату Т</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>14:23, 1 раз, 14:23</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Справочник.РегламентныеПериоды + Документ.ПланРегламентныхОперацийДУ</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I26" s="14" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="K26" s="14" t="n">
-        <v>601</v>
-      </c>
-      <c r="L26" s="14" t="n">
-        <v>667</v>
-      </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="I26" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>333</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N26" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P26" s="13" t="inlineStr">
-        <is>
-          <t>На полном объёме базы зафиксирован один прогон - точность оценки ограничена.</t>
+      <c r="N26" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>Замер на ПРОД ещё до выкладки IMDEV-8863.1. Длительность пересчитана с ускорением x2 по эффекту той же доработки на вечерних регламентах. На полном объёме зафиксирован один прогон - точность оценки ограничена.</t>
         </is>
       </c>
     </row>
@@ -2015,70 +2030,68 @@
       <c r="P27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Начисление вознаграждения</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Ежеквартально</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>-, 1 раз/квартал, -</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>внНачислениеВознаграждения_РозничноеДУ</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>ПРОД</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n">
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>DR (IMDEV-9153)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I28" s="14" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>635</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <v>635</v>
-      </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="I28" s="9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>646</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>789</v>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N28" s="10" t="n">
-        <v>189</v>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
+      <c r="N28" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="P28" s="13" t="inlineStr">
-        <is>
-          <t>ОЦЕНОЧНО: массового квартального прогона в выгрузке нет, есть только единичные договоры. Длительность пересчитана от удельной стоимости одного договора на всю базу с учётом 12 потоков. Требуется замер квартального прогона.</t>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>Замер полного объёма из IMDEV-9153 (DR): 1 ч 04 мин 34 сек на 20 467 договоров после параллельной оптимизации. Последовательно было 9 ч 52 мин. В ПРОД-выгрузке ЗамерыВремени массового квартального прогона нет.</t>
         </is>
       </c>
     </row>
@@ -2159,77 +2172,83 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>Ежеквартально</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>17:00, 1 раз, 17:00</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>внОтчетУправляющегоДУсогласно482П_v15 + внЗапускПоРасписаниюОтчетаУправляющегоДУ</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="H30" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="I30" s="14" t="n">
-        <v>565</v>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="I30" s="29" t="inlineStr">
+        <is>
+          <t>4.7 (ср. 20 дог./день)</t>
+        </is>
+      </c>
+      <c r="J30" s="29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K30" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="14" t="n">
-        <v>5652</v>
-      </c>
-      <c r="L30" s="14" t="n">
-        <v>5652</v>
-      </c>
-      <c r="M30" s="12" t="inlineStr">
+      <c r="L30" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N30" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="25" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="P30" s="13" t="inlineStr">
-        <is>
-          <t>ОЦЕНОЧНО, НИЖНЯЯ ГРАНИЦА: показано время на ВСЕ договоры РДУ. Один замер в регистре - это один отчёт по одному договору (в ДопИнф стоит конкретный ДоговорДУ, вес = 1), таких замеров 966. Квартальный прогон обходит весь пул "Розничное ДУ", то есть строит по отчёту на договор. Расчёт: 25 тыс. отчётов по 13,6 с при 10 потоках. Это нижняя граница: при конкуренции за ресурсы время одного отчёта вырастет. Замер массового прогона в коде УЖЕ ЕСТЬ (ключ "Отчет Управляющего ДУ 482П РозничноеДУ выгрузка", вес = число договоров), но в выгрузке его нет - в окно 28.07-02.09 квартальный прогон не попал. Нужна выгрузка за начало квартала, а не доработка кода.</t>
+      <c r="P30" s="28" t="inlineStr">
+        <is>
+          <t>Показано среднее за день по поштучным замерам (не полный квартальный прогон). Ср. 4.7 мин/день, ср. 20 договоров/день. Прогноз и предел не указываются до квартальной выгрузки массового ключа ("Отчет Управляющего ДУ 482П РозничноеДУ выгрузка").</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Дополнительно выявлено (в списке руководителя не было)</t>
+          <t>Дополнительно выявлено (в списке технического архитектора не было)</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -2249,281 +2268,213 @@
       <c r="P31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Выгрузка данных в кабинет клиента ДУ (экспорт HNWI)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>10:00, 10 мин, 23:52</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>внЭкспортДанныхКабиентHNWI_DU</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="14" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="14" t="n">
         <v>0.96</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="14" t="n">
         <v>0.22</v>
       </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O32" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P32" s="8" t="inlineStr">
+      <c r="P32" s="13" t="inlineStr">
         <is>
           <t>Аналог узкого места МО (выгрузка в кабинет клиента). Здесь работает инкрементально каждые 10 минут, поэтому длительность одного прогона мала, но есть прогоны до 79 минут.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Распределение доходов по ценным бумагам</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>15:00, 1 раз, 15:00</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>внРаспределениеДоходовПоЦеннымБумагам</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="14" t="n">
         <v>15.7</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="14" t="n">
         <v>15.7</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="14" t="n">
         <v>157</v>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="N33" s="10" t="n">
         <v>765</v>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
+      <c r="P33" s="13" t="inlineStr">
         <is>
           <t>В выгрузке всего один замер - статистика недостаточна.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Расчёт вознаграждения РДУ (ожидаемые платежи)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>8:00, 1 раз, 8:00</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>внРасчетВознагражденияРозничногоДУ</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" s="14" t="n">
         <v>0.19</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="14" t="n">
         <v>0.33</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="14" t="n">
         <v>1.9</v>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L34" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="M34" s="12" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>&gt; 1 000</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O34" s="10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P34" s="8" t="inlineStr">
+      <c r="P34" s="13" t="inlineStr">
         <is>
           <t>В наблюдаемом периоде ДоговоровКРасчету = 0, то есть замерено холостое прохождение. Нагрузочная оценка требует прогона в квартальную дату.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Отчёт по отрицательным остаткам на РС</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Ежедневно</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>10:53, 1 раз, 10:53</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>внОтрицательныеОстаткиНаАналитическомСчете</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>ПРОД</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>&gt; 1 000</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>Ручной отчёт, работает быстро.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:P35"/>
+  <autoFilter ref="A3:P34"/>
   <mergeCells count="9">
     <mergeCell ref="A13:P13"/>
     <mergeCell ref="A1:P1"/>
@@ -2545,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2560,290 +2511,278 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Исполнение сделок (авто закрытие Т-1, Т-2)</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Слабо зависит от числа договоров. Объём работы - число сделок за день (порции нарезаются по ДоговорДУ, но длительность задают сделки). Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Объём - число сделок за день. Допущение: средняя интенсивность сделок на договор постоянна, поэтому при росте базы x10 объём сделок тоже x10. По замерам: медиана ~19 600 сделок/день (~0,79 на договор базы; ~11,6 на договор с активностью в прогоне). Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Загрузка сделок за дату Т, открытие плановой позиции сделок Т по РДУ</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Слабо зависит от числа договоров. Объём - число сделок за день. Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Сеанс идёт несколько раз в день, окно между сеансами. Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Объём - число сделок за день. Допущение: интенсивность сделок на договор постоянна, база x10 -&gt; сделки x10. По замерам создание: медиана ~5 700 сделок/день (~0,23 на договор базы). Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Сеанс идёт несколько раз в день, окно между сеансами. Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Обработка отчётов брокера за Т-1</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 1014 строк отчёта. Зависимость от базы: Объём - строки отчёта брокера (СтрокSQL), растут с числом договоров. Потоки: КоличествоПотоков = 6 задано жёстко в коде; ограничение "один договор - один поток" не позволяет поднять без переработки. Окно: Старт 05:05, до начала операционного дня 09:00. Ключевые операции регистра: Д у. пакетный отчет брокера. получение s q l. фоновое выполнение; Д у. пакетный отчет брокера. создание операций. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Загрузка выписок банка</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 26 дням. Замеров в выгрузке: 26. Типовой объём замера: 2 платежей. Зависимость от базы: Группы нарезаются по паре (БанковскийСчет, ДоговорДУ); объём - выписки и платежи. Потоки: Реквизит МаксПараллельныхГрупп, по умолчанию 3. Резерв по потокам: Предел - число групп (БанковскийСчет, ДоговорДУ), с ростом базы он только растёт. Пул можно поднять настройкой без доработки кода. Окно: Операционное утро, до 10:00. Ключевые операции регистра: Д у. загрузка выписок. получение w e b_ v t b. заполнить w e b_ v t b; Д у. загрузка выписок. разбор выписок. заполнить w e b_ v t b; Д у. загрузка выписок. создание документов. разобрать отмеченные.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Сверка денежных средств</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 расхождений. Зависимость от базы: Строки результата - комбинации ДоговорДУ + Счёт + Валюта из базы. Потоки: Один SQL-запрос с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Сверка денежных средств ЕРС</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 счетов с расхождением. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 2 счетов с расхождением -&gt; 2 с (n=2) и 3 счетов с расхождением -&gt; 9 с (n=3), то есть 6.6030 с на единицу плюс постоянные 0 с. Зависимость от базы: Сверяются итоги по 10 жёстко заданным счётам ЕРС, а не каждый договор. Число счетов от клиентской базы не зависит. Потоки: Цикл по фиксированному списку 10 счетов ЕРС. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств е р с. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Перевод денежных средств на биржу (формирование п/п) датой Т</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 6119 замерам. Замеров в выгрузке: 6119. Типовой объём замера: 1 поручений. Зависимость от базы: Вес замера - число поручений, растёт с числом договоров. Потоки: Последовательная синхронизация с 1С:ДО, пула потоков нет. Окно: Запуск каждые 5-10 минут. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение поручения.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Загрузка котировок 1-й сеанс за дату Т-1</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов (около 3 600 котировок), от числа договоров РДУ не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Сверка загрузки котировок</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 302 строк отчёта. Зависимость от базы: Строки отчёта - инструменты (Актив x Биржа), около 300 строк. Потоки: Один запрос, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. контроль котировок. отчет. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Загрузка котировок финальная за Т-1</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов, от числа договоров не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Сверка с отчётом брокера</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 35 замерам. Замеров в выгрузке: 35. Типовой объём замера: 7989 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1087 сделок -&gt; 163 с (n=7) и 8536 сделок -&gt; 997 с (n=26), то есть 0.1120 с на единицу плюс постоянные 41 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Окно сверки не менее 60 минут (старт 08:45). Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое проведение.</t>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 104 замерам. Замеров в выгрузке: 104. Типовой объём замера: 8052 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 8631 сделок -&gt; 112 с (n=75) и 18509 сделок -&gt; 310 с (n=2), то есть 0.0200 с на единицу плюс постоянные 0 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Окно сверки не менее 60 минут (старт 08:45). Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Сверка остатков ЦБ с депозитарием</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 строк сверки. Зависимость от базы: Строки сверки - ДоговорДУ x ЦБ, сейчас около 121 000 строк. Потоки: Один SQL с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка ц б. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Сверка API сигнал vs Реестры платежей</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: замер в код не вставлен. Зависимость от базы: По смыслу зависит от числа платежей, то есть от клиентской базы. Потоки: Операция не реализована, замера в коде нет. Окно: Окно сверки не менее 60 минут.</t>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 9 замерам. Замеров в выгрузке: 9. Типовой объём замера: 1 строк с минусом. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1 строк с минусом -&gt; 0 с (n=8) и 38 строк с минусом -&gt; 1 с (n=1), то есть 0.0077 с на единицу плюс постоянные 0 с. Зависимость от базы: Группировка АналитическийСчет + ДоговорДУ + Валюта по пулу Розничное ДУ. Потоки: Один запрос ОСВ, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка. отрицательные остатки на р с. формирование отчета. ручной.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Процесс расторжения РДУ</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 3398 замерам. Замеров в выгрузке: 3398. Типовой объём замера: 137 договоров. Зависимость от базы: Вес замера - число договоров к расторжению из 1С:ДО. Потоки: Последовательная обработка договоров, пула потоков нет. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. расторжение договоров р д у. фоновое договоры из д о к расторжению.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Загрузка договоров РДУ за дату Т, карточки клиента, автозаполнение аналитики для ВУ</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 3607 замерам. Замеров в выгрузке: 3607. Типовой объём замера: 1 объектов НСИ. Зависимость от базы: Объём - новые объекты НСИ (договоры, карточки), поток растёт с базой. Потоки: Последовательный обмен с 1С:ДО, распараллеливание не предусмотрено. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение.</t>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 3607 замерам; средний вес замера 1.23, прогноз от веса x10. Замеров в выгрузке: 3607. Типовой объём замера: 1 новых объектов НСИ. Модель роста: поток новинок: средний вес замера 1.23 новых объектов НСИ, 75.61 с на единицу; прогноз на средний вес x10 = 12.33. Зависимость от базы: Грузятся только новые договоры/карточки НСИ. Объём - средний вес замера (поток новинок); при росте базы в 10 раз средний поток новинок тоже вырастет примерно в 10 раз. Потоки: Последовательный обмен с 1С:ДО, распараллеливание не предусмотрено. Окно: Окно не более 30 минут (запуск каждые 10 минут по расписанию). Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>Вечерние регламентные операции, расчёт РСА/СЧА за Т-1</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 3 замерам. Замеров в выгрузке: 3. Типовой объём замера: 21994 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3087 договоров -&gt; 1274 с (n=4) и 21994 договоров -&gt; 2542 с (n=3), то есть 0.0671 с на единицу плюс постоянные 1067 с. Зависимость от базы: Прямой перебор договоров РДУ: пачки по 3 000, чанки по 50 договоров на поток. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999, жёсткого предела в коде нет - резерв ограничен только ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. регламентные операции.2. вечерние операции.</t>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 3 замерам. Замеров в выгрузке: 3. Типовой объём замера: 21994 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3087 договоров -&gt; 1274 с (n=4) и 21994 договоров -&gt; 2542 с (n=3), то есть 0.0671 с на единицу плюс постоянные 1067 с. Зависимость от базы: Прямой перебор договоров РДУ: пачки по 3 000, чанки по 50 договоров на поток. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999, жёсткого предела в коде нет - резерв ограничен только ресурсами кластера. Окно: Окно не более 3 часов (180 минут). Ключевые операции регистра: Д у. регламентные операции.2. вечерние операции.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Утренние регламентные операции, начисления % по депозитам, РЕПО, НКД, погашения за дату Т</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 22889 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3090 договоров -&gt; 437 с (n=27) и 22889 договоров -&gt; 3606 с (n=1), то есть 0.1601 с на единицу плюс постоянные 0 с. Зависимость от базы: Прямой перебор договоров РДУ, тот же диспетчер пачек, что у вечерних. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999 - резерв ограничен ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. регламентные операции.1. утренние операции.</t>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 1 замерам; с ускорением x2.0 (IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.). Замеров в выгрузке: 1. Типовой объём замера: 22889 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3090 договоров -&gt; 437 с (n=27) и 22889 договоров -&gt; 3606 с (n=1), то есть 0.1601 с на единицу плюс постоянные 0 с учтено ускорение x2.0: IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.. Зависимость от базы: Прямой перебор договоров РДУ, тот же диспетчер пачек, что у вечерних. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999 - резерв ограничен ресурсами кластера. Окно: Окно не более 3 часов (180 минут). Ключевые операции регистра: Д у. регламентные операции.1. утренние операции.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>Начисление вознаграждения</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: пересчёт от удельной стоимости договора. Замеров в выгрузке: 253. Типовой объём замера: 1 договоров. Модель роста: удельная стоимость одного договора 1.83 с, при 12 потоках это 0.152 с на договор; развёрнуто на всю базу. Зависимость от базы: Вес замера - число договоров к начислению. Потоки: Пул фоновых заданий, лимит из константы (12), пачки по 100 договоров зашиты в коде. Резерв по потокам: Лимит берётся из той же константы, что у регламентов - резерв ограничен ресурсами кластера. Окно: Квартальное закрытие, ночное окно. Ключевые операции регистра: Д у. начисление вознаграждения р д у. начисление. ручной; Д у. начисление вознаграждения р д у. начисление. начисление вознаграждения при расторжении розничное д у фоновое.</t>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: замер полного объёма: IMDEV-9153 DR 30.09.2026: параллельное начисление, пачки по 100, ~12 потоков; было последовательно 9 ч 52 мин 44 сек на 20 482 договоров. Замеров в выгрузке: 1. Типовой объём замера: 20467 договоров. Модель роста: удельная стоимость по замеру полного объёма: 20467 договоров -&gt; 3874 с (0.1893 с на договор). Зависимость от базы: Вес замера - число договоров к начислению. Потоки: Пул фоновых заданий, лимит из константы (12), пачки по 100 договоров зашиты в коде. Резерв по потокам: Лимит берётся из той же константы, что у регламентов - резерв ограничен ресурсами кластера. Окно: Квартальное закрытие, ночное окно. Ключевые операции регистра: Д у. начисление вознаграждения р д у. начисление. ручной; Д у. начисление вознаграждения р д у. начисление. начисление вознаграждения при расторжении розничное д у фоновое.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Оплата вознаграждения</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Длительность: замер в код не вставлен. Зависимость от базы: Отбор договоров РДУ, объём прямо пропорционален базе. Потоки: Последовательный перебор строк ДокументыКВыгрузке, пула потоков нет. Окно: Квартальное закрытие, ночное окно.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: пересчёт от удельной стоимости договора. Замеров в выгрузке: 552. Типовой объём замера: 1 договоров. Модель роста: удельная стоимость одного договора 13.56 с, при 10 потоках это 1.357 с на договор; развёрнуто на всю базу. Зависимость от базы: Регламент обрабатывает очередь регистра СостоянияВыгрузкиОтчетовДУ. Очередь пополняется, когда пуста: квартально - всем пулом "Розничное ДУ", плюс ежедневно договорами с датой окончания. То есть квартальный прогон - это один отчёт на каждый договор РДУ. Потоки: Реквизит Отчет.КоличествоПотоков. В обработчиках формы стоит жёсткая отсечка: если больше 10, значение сбрасывается в 10. Многопоточность работает только в режиме "по клиентам розничного ДУ в фоновых потоках" (РежимРаботы=2) - именно он используется регламентом. Окно: Ночное окно 8 часов после старта 17:00. Ключевые операции регистра: Отчет управляющего д у 482 п.</t>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Длительность: среднее за день: 4.7 мин, среднее к-во договоров/день: 20; полный квартальный прогон в выгрузке отсутствует - прогноз не публикуется. Замеров в выгрузке: 27. Типовой объём замера: 20 договоров/день. Зависимость от базы: Регламент обрабатывает очередь регистра СостоянияВыгрузкиОтчетовДУ. Очередь пополняется, когда пуста: квартально - всем пулом "Розничное ДУ", плюс ежедневно договорами с датой окончания. То есть квартальный прогон - это один отчёт на каждый договор РДУ. Потоки: Реквизит Отчет.КоличествоПотоков. В обработчиках формы стоит жёсткая отсечка: если больше 10, значение сбрасывается в 10. Многопоточность работает только в режиме "по клиентам розничного ДУ в фоновых потоках" (РежимРаботы=2) - именно он используется регламентом. Окно: Ночное окно 8 часов после старта 17:00. Ключевые операции регистра: Отчет управляющего д у 482 п.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Выгрузка данных в кабинет клиента ДУ (экспорт HNWI)</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 2944 замерам. Замеров в выгрузке: 2944. Типовой объём замера: 1 клиентов и дат. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3 клиентов и дат -&gt; 8 с (n=149) и 5 клиентов и дат -&gt; 10 с (n=386), то есть 0.7648 с на единицу плюс постоянные 6 с. Зависимость от базы: Вес замера - клиенты и даты инвестирования. Потоки: Последовательная выгрузка, ограничение на стороне принимающей системы (кабинет). Окно: Инкрементальный запуск каждые 10 минут. Ключевые операции регистра: Д у. экспорт h n w i. выгрузка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Распределение доходов по ценным бумагам</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 13361 строк НКД. Зависимость от базы: Объём - отмеченные строки НКД/погашений/дивидендов по позициям договоров. Потоки: Лимит из константы МаксимальноеКоличествоПараллельныхПотоков (12), пачки по 100 строк. Резерв по потокам: Резерв ограничен ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. распределение доходов. создание операций.вн распределение доходов по ценным бумагам.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Расчёт вознаграждения РДУ (ожидаемые платежи)</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 договоров к расчёту. Зависимость от базы: Отбор договоров пула Розничное ДУ. Потоки: Последовательный перебор ДоговорыДУКРасчету. Окно: Старт 08:00, до начала операционного дня. Ключевые операции регистра: Д у. расчет вознаграждения р д у. расчет. фоновое выполнение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Отчёт по отрицательным остаткам на РС</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 9 замерам. Замеров в выгрузке: 9. Типовой объём замера: 1 строк с минусом. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1 строк с минусом -&gt; 0 с (n=8) и 38 строк с минусом -&gt; 1 с (n=1), то есть 0.0077 с на единицу плюс постоянные 0 с. Зависимость от базы: Группировка АналитическийСчет + ДоговорДУ + Валюта по пулу Розничное ДУ. Потоки: Один запрос ОСВ, распараллеливание не предусмотрено. Окно: Принято по аналогии с прочими сверками. Ключевые операции регистра: Д у. сверка. отрицательные остатки на р с. формирование отчета. ручной.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2866,176 +2805,188 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Подсветка строки</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr"/>
+      <c r="B1" s="31" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Красный</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Предел ниже целевых 250 тыс. договоров - операция не выдержит рост базы.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Жёлтый</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Предел от 250 до 500 тыс. договоров - запас менее двукратного.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Зелёный</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Запас достаточный либо операция не зависит от числа клиентов.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Оранжевый</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Нет квартальной выгрузки массового прогона: показано среднее за день и среднее число договоров/день; прогноз и предел не публикуются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Серый</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Замер в код не вставлен: длительность и прогноз не рассчитываются (прочерк).</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="inlineStr"/>
-      <c r="B6" s="26" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr"/>
+      <c r="B7" s="31" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Длительность сейчас</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Медиана прогонов на полном объёме базы: только регламентный контур, вес замера от 15 тыс. договоров, аварийные замеры исключены.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Длительность макс</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Максимум длительности среди тех же отобранных замеров (полный объём, без аварийных).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Время запуска</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>По фактическим замерам: первое типичное время старта за день, частота запусков, последнее типичное время старта. Формат: ЧЧ:ММ, N мин (или 1 раз), ЧЧ:ММ.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Прогноз x10 линейный</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Текущая длительность, умноженная на 10. Не применяется к операциям, не зависящим от числа договоров (котировки, счета ЕРС, загрузка/исполнение сделок).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Текущая длительность, умноженная на 10. Для загрузки/исполнения сделок применяется по допущению: интенсивность сделок на договор постоянна. Не применяется к операциям, не зависящим от числа договоров (котировки, счета ЕРС).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Прогноз расчётный</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Линейная модель ПостояннаяЧасть + СтоимостьЕдиницы * Объём. Наклон по двум самым крупным уровням объёма из фактических замеров.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Потоков макс</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Только предел, подтверждённый кодом: жёсткое значение, ограничение интерфейса или значение константы. Где предел упирается в ресурсы кластера, а не в код, максимум приравнен к текущему значению, а резерв описан на листе "Методика и детали".</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Предел, тыс. договоров</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Число договоров, при котором операция упирается в своё окно выполнения. Для загрузки/исполнения сделок - "от сделок" (окно исполнения: 2 ч на 200 тыс. сделок).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Число договоров, при котором операция упирается в своё окно выполнения. Для сделок - через пересчёт объёма сделок при постоянной интенсивности на договор (окно исполнения: 2 ч на 200 тыс. сделок).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Пометка "оценка"</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Массового прогона в выгрузке нет, цифра получена пересчётом от удельной стоимости договора. Требуется замер массового прогона.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Пометка "нет замеров"</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Замер в код не вставлен. Расчёт по аналогии не делается - в ячейках прочерк.</t>
         </is>

--- a/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
@@ -636,7 +636,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 03.09.2026 14:47</t>
+          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 04.09.2026 14:58</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="N5" s="5" t="n">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>Прогноз x10 применён по допущению: сделок на договор не меняется, база x10 -&gt; сделки x10. Потоков сейчас 6. При ~196 тыс. сделок/день на 250 тыс. договоров упирается и в окно 2 ч, и в лимит 200 тыс. сделок.</t>
+          <t>Предел линейно от худшего замера (1 сделка = 1 договор). Потоков сейчас 6.</t>
         </is>
       </c>
     </row>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>Прогноз x10 применён по допущению постоянной интенсивности сделок на договор. Получение из Tibco - 1 поток; создание на ПРОД - 3 потока.</t>
+          <t>Предел линейно от худшего цикла (1 сделка = 1 договор). Получение из Tibco - 1 поток; создание на ПРОД - 3 потока.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Объём - число сделок за день. Допущение: средняя интенсивность сделок на договор постоянна, поэтому при росте базы x10 объём сделок тоже x10. По замерам: медиана ~19 600 сделок/день (~0,79 на договор базы; ~11,6 на договор с активностью в прогоне). Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
+          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Объём - число сделок. Допущение: при росте базы x10 сделки в среднем тоже x10; вес "сделки" для предела считаем как "договоры" (1 сделка = 1 договор). Худший замер: 25 119 сделок за 69,8 мин. Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Объём - число сделок за день. Допущение: интенсивность сделок на договор постоянна, база x10 -&gt; сделки x10. По замерам создание: медиана ~5 700 сделок/день (~0,23 на договор базы). Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Сеанс идёт несколько раз в день, окно между сеансами. Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Объём - число сделок. Допущение: при росте базы x10 сделки в среднем тоже x10; вес "сделки" для предела считаем как "договоры" (1 сделка = 1 договор). Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Окно 2 часа (как у исполнения сделок). Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
         </is>
       </c>
     </row>

--- a/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-9393 Создать общую таблицу текущей длительности ключевых операций/Документация/KeyOperationsDuration.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9ECEF"/>
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
+        <fgColor rgb="00E9ECEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,21 +196,6 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -226,9 +211,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -241,10 +223,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -636,7 +618,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 04.09.2026 14:58</t>
+          <t>IMDEV-9393. Длительность ключевых операций Розничного ДУ (ДУ 1.5). Рост 25 тыс. -&gt; 250 тыс. договоров. Сформировано 07.09.2026 13:21</t>
         </is>
       </c>
     </row>
@@ -780,16 +762,16 @@
         <v>6</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>69.8</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -797,7 +779,7 @@
         </is>
       </c>
       <c r="N5" s="5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -806,7 +788,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>Предел линейно от худшего замера (1 сделка = 1 договор). Потоков сейчас 6.</t>
+          <t>Предел с учётом K=0,865 (сделки/договор). Потоков сейчас 6.</t>
         </is>
       </c>
     </row>
@@ -852,7 +834,7 @@
         <v>29.3</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -865,7 +847,7 @@
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -874,7 +856,7 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>Предел линейно от худшего цикла (1 сделка = 1 договор). Получение из Tibco - 1 поток; создание на ПРОД - 3 потока.</t>
+          <t>Предел с учётом K=0,251 (созданные сделки/договор). Получение из Tibco - 1 поток; создание на ПРОД - 3 потока.</t>
         </is>
       </c>
     </row>
@@ -914,13 +896,13 @@
         <v>6</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>15.1</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>34.9</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
@@ -986,7 +968,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>9:09, 1 раз, 9:09</t>
+          <t>9:08, 1 раз, 9:08</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1006,13 +988,13 @@
         <v>3</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>73.3</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
@@ -1025,7 +1007,7 @@
         </is>
       </c>
       <c r="N9" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
@@ -1080,7 +1062,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
@@ -1093,7 +1075,7 @@
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="O10" s="15" t="inlineStr">
         <is>
@@ -1302,16 +1284,16 @@
         <v>1</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J14" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
@@ -1493,66 +1475,66 @@
       <c r="P17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Сверка с отчётом брокера</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Ежедневно</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>9:00, 60 мин, 12:00</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>внСверкаCделокДУСОтчетомБрокера</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="14" t="n">
+      <c r="I18" s="19" t="n">
         <v>1.7</v>
       </c>
-      <c r="J18" s="14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K18" s="14" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L18" s="14" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="J18" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>Да (через сделки)</t>
         </is>
       </c>
-      <c r="N18" s="10" t="n">
-        <v>558</v>
-      </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="N18" s="15" t="n">
+        <v>491</v>
+      </c>
+      <c r="O18" s="15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P18" s="13" t="inlineStr">
+      <c r="P18" s="18" t="inlineStr">
         <is>
           <t>Однопоточная. В расчёт берётся только контур без проведения ("фоновое выполнение", РДУ). Контур с проведением ("фоновое проведение") - для сделок НЕ РДУ, в расчётах не учитывается (он примерно в 9 раз тяжелее и к Розничному ДУ не относится).</t>
         </is>
@@ -1594,13 +1576,13 @@
         <v>1</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>7.3</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="L19" s="19" t="inlineStr">
         <is>
@@ -1613,7 +1595,7 @@
         </is>
       </c>
       <c r="N19" s="15" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O19" s="15" t="inlineStr">
         <is>
@@ -1733,7 +1715,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>7:00, 10 мин, 22:52</t>
+          <t>7:00, 10 мин, 22:53</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -1756,7 +1738,7 @@
         <v>0.02</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="K22" s="14" t="n">
         <v>0.18</v>
@@ -1823,16 +1805,16 @@
         <v>1</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" s="19" t="n">
         <v>7.3</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="M23" s="17" t="inlineStr">
         <is>
@@ -1840,7 +1822,7 @@
         </is>
       </c>
       <c r="N23" s="15" t="n">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="O23" s="15" t="inlineStr">
         <is>
@@ -1891,7 +1873,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>11:46, 1 раз, 11:46</t>
+          <t>11:47, 1 раз, 11:47</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2096,152 +2078,144 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>Оплата вознаграждения</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Оплата вознаграждения (Оплата КЗ)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Ежеквартально</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>6:19, 1 раз, 6:19</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>внОплатаКЗПоКлиентамРДУ</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Разработческая база (ЗамерыРазраб)</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>внОплатаКЗПоКлиентамРДУ (замер не реализован)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>667</v>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>Замер блокировки ДС: 9 213 договоров за 6.6 мин. Остальные этапы цепочки (поручения, поступление, списание) в выгрузке только на 7 договорах - в длительность полного объёма пока не включены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Ежеквартально</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>17:00, 1 раз, 17:00</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>внОтчетУправляющегоДУсогласно482П_v15 + внЗапускПоРасписаниюОтчетаУправляющегоДУ</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>ПРОД</t>
         </is>
       </c>
-      <c r="G29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="J29" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="L29" s="24" t="inlineStr">
-        <is>
-          <t>нет замеров</t>
-        </is>
-      </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="G30" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>4.8 (ср. 21 дог./день)</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="N29" s="20" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O29" s="20" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="P29" s="23" t="inlineStr">
-        <is>
-          <t>Замер в код внОплатаКЗПоКлиентамРДУ не вставлен. Длительность и прогноз не рассчитываются - в таблице прочерк. Нужно добавить замер в обработку.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>Ежеквартально</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>17:00, 1 раз, 17:00</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>внОтчетУправляющегоДУсогласно482П_v15 + внЗапускПоРасписаниюОтчетаУправляющегоДУ</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>ПРОД</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="29" t="inlineStr">
-        <is>
-          <t>4.7 (ср. 20 дог./день)</t>
-        </is>
-      </c>
-      <c r="J30" s="29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K30" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" s="27" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="N30" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="25" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P30" s="28" t="inlineStr">
-        <is>
-          <t>Показано среднее за день по поштучным замерам (не полный квартальный прогон). Ср. 4.7 мин/день, ср. 20 договоров/день. Прогноз и предел не указываются до квартальной выгрузки массового ключа ("Отчет Управляющего ДУ 482П РозничноеДУ выгрузка").</t>
+      <c r="P30" s="23" t="inlineStr">
+        <is>
+          <t>Показано среднее за день по поштучным замерам (не полный квартальный прогон). Ср. 4.8 мин/день, ср. 21 договоров/день. Прогноз и предел не указываются до квартальной выгрузки массового ключа ("Отчет Управляющего ДУ 482П РозничноеДУ выгрузка").</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2283,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
@@ -2511,278 +2485,278 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Исполнение сделок (авто закрытие Т-1, Т-2)</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 19 замерам. Замеров в выгрузке: 19. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2407 с (n=18) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0459 с на единицу плюс постоянные 1515 с. Зависимость от базы: Объём - число сделок. Допущение: при росте базы x10 сделки в среднем тоже x10; вес "сделки" для предела считаем как "договоры" (1 сделка = 1 договор). Худший замер: 25 119 сделок за 69,8 мин. Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 21 замерам. Замеров в выгрузке: 21. Типовой объём замера: 19644 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 19420 сделок -&gt; 2344 с (n=20) и 36247 сделок -&gt; 3180 с (n=1), то есть 0.0497 с на единицу плюс постоянные 1380 с. Зависимость от базы: Объём - число сделок. Коэф. к договорам K=сделки/договоры базы дня (медиана по дням с вечерними регламентами) = 0,865. Сделки@250к = 250000*K. Худший замер: 25119 сделок. Потоки: Настройка КоличествоПотоков, в замерах фиксируется Потоков=6. Резерв по потокам: Жёсткого предела в коде нет - потоки можно поднять настройкой, но ускорение замером не подтверждено. Окно: Не более 2 часов на 200 тыс. сделок. Ключевые операции регистра: Д у. исполнение сделок т+n. исполнение в потоках. фоновое выполнение_ потоковое исполнение сделок.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Загрузка сделок за дату Т, открытие плановой позиции сделок Т по РДУ</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 38 дням. Замеров в выгрузке: 38. Типовой объём замера: 359 сделок. Зависимость от базы: Объём - число сделок. Допущение: при росте базы x10 сделки в среднем тоже x10; вес "сделки" для предела считаем как "договоры" (1 сделка = 1 договор). Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Окно 2 часа (как у исполнения сделок). Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 41 дням. Замеров в выгрузке: 41. Типовой объём замера: 260 сделок. Зависимость от базы: Объём - созданные сделки. Коэф. K=созданные_сделки/договоры базы дня (медиана) = 0,251. Сделки@250к = 250000*K. Потоки: Получение из Tibco - строго однопоточное (один WS-вызов). Создание сделок параллелится по пачкам договоров: на ПРОД КоличествоПотоков = 3. Резерв по потокам: Число потоков создания сделок задаётся настройкой, жёсткого предела в коде нет - резерв есть, но ускорение замером не подтверждено. Окно: Окно 2 часа (как у исполнения сделок). Ключевые операции регистра: Д у. загрузка сделок. получение tibco. фоновое выполнение; Д у. загрузка сделок. создание сделок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Обработка отчётов брокера за Т-1</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 1014 строк отчёта. Зависимость от базы: Объём - строки отчёта брокера (СтрокSQL), растут с числом договоров. Потоки: КоличествоПотоков = 6 задано жёстко в коде; ограничение "один договор - один поток" не позволяет поднять без переработки. Окно: Старт 05:05, до начала операционного дня 09:00. Ключевые операции регистра: Д у. пакетный отчет брокера. получение s q l. фоновое выполнение; Д у. пакетный отчет брокера. создание операций. фоновое выполнение.</t>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 40 дням. Замеров в выгрузке: 40. Типовой объём замера: 936 строк отчёта. Зависимость от базы: Объём - строки отчёта брокера (СтрокSQL), растут с числом договоров. Потоки: КоличествоПотоков = 6 задано жёстко в коде; ограничение "один договор - один поток" не позволяет поднять без переработки. Окно: Старт 05:05, до начала операционного дня 09:00. Ключевые операции регистра: Д у. пакетный отчет брокера. получение s q l. фоновое выполнение; Д у. пакетный отчет брокера. создание операций. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Загрузка выписок банка</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 26 дням. Замеров в выгрузке: 26. Типовой объём замера: 2 платежей. Зависимость от базы: Группы нарезаются по паре (БанковскийСчет, ДоговорДУ); объём - выписки и платежи. Потоки: Реквизит МаксПараллельныхГрупп, по умолчанию 3. Резерв по потокам: Предел - число групп (БанковскийСчет, ДоговорДУ), с ростом базы он только растёт. Пул можно поднять настройкой без доработки кода. Окно: Операционное утро, до 10:00. Ключевые операции регистра: Д у. загрузка выписок. получение w e b_ v t b. заполнить w e b_ v t b; Д у. загрузка выписок. разбор выписок. заполнить w e b_ v t b; Д у. загрузка выписок. создание документов. разобрать отмеченные.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 28 дням. Замеров в выгрузке: 28. Типовой объём замера: 2 платежей. Зависимость от базы: Группы нарезаются по паре (БанковскийСчет, ДоговорДУ); объём - выписки и платежи. Потоки: Реквизит МаксПараллельныхГрупп, по умолчанию 3. Резерв по потокам: Предел - число групп (БанковскийСчет, ДоговорДУ), с ростом базы он только растёт. Пул можно поднять настройкой без доработки кода. Окно: Операционное утро, до 10:00. Ключевые операции регистра: Д у. загрузка выписок. получение w e b_ v t b. заполнить w e b_ v t b; Д у. загрузка выписок. разбор выписок. заполнить w e b_ v t b; Д у. загрузка выписок. создание документов. разобрать отмеченные.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Сверка денежных средств</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 расхождений. Зависимость от базы: Строки результата - комбинации ДоговорДУ + Счёт + Валюта из базы. Потоки: Один SQL-запрос с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств. сверка. фоновое выполнение.</t>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 28 замерам. Замеров в выгрузке: 28. Типовой объём замера: 1 расхождений. Зависимость от базы: Строки результата - комбинации ДоговорДУ + Счёт + Валюта из базы. Потоки: Один SQL-запрос с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Сверка денежных средств ЕРС</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 счетов с расхождением. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 2 счетов с расхождением -&gt; 2 с (n=2) и 3 счетов с расхождением -&gt; 9 с (n=3), то есть 6.6030 с на единицу плюс постоянные 0 с. Зависимость от базы: Сверяются итоги по 10 жёстко заданным счётам ЕРС, а не каждый договор. Число счетов от клиентской базы не зависит. Потоки: Цикл по фиксированному списку 10 счетов ЕРС. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств е р с. сверка. фоновое выполнение.</t>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 40 замерам. Замеров в выгрузке: 40. Типовой объём замера: 1 счетов с расхождением. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 2 счетов с расхождением -&gt; 2 с (n=4) и 3 счетов с расхождением -&gt; 9 с (n=3), то есть 6.6000 с на единицу плюс постоянные 0 с. Зависимость от базы: Сверяются итоги по 10 жёстко заданным счётам ЕРС, а не каждый договор. Число счетов от клиентской базы не зависит. Потоки: Цикл по фиксированному списку 10 счетов ЕРС. Окно: Окно сверки не менее 60 минут (ранее цель IMDEV-8927: 6 минут). Ключевые операции регистра: Д у. сверка денежных средств е р с. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Перевод денежных средств на биржу (формирование п/п) датой Т</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 6119 замерам. Замеров в выгрузке: 6119. Типовой объём замера: 1 поручений. Зависимость от базы: Вес замера - число поручений, растёт с числом договоров. Потоки: Последовательная синхронизация с 1С:ДО, пула потоков нет. Окно: Запуск каждые 5-10 минут. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение поручения.</t>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 6813 замерам. Замеров в выгрузке: 6813. Типовой объём замера: 1 поручений. Зависимость от базы: Вес замера - число поручений, растёт с числом договоров. Потоки: Последовательная синхронизация с 1С:ДО, пула потоков нет. Окно: Запуск каждые 5-10 минут. Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение поручения.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Загрузка котировок 1-й сеанс за дату Т-1</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов (около 3 600 котировок), от числа договоров РДУ не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 40 дням. Замеров в выгрузке: 40. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов (около 3 600 котировок), от числа договоров РДУ не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Сверка загрузки котировок</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 302 строк отчёта. Зависимость от базы: Строки отчёта - инструменты (Актив x Биржа), около 300 строк. Потоки: Один запрос, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. контроль котировок. отчет. фоновое выполнение.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 28 замерам. Замеров в выгрузке: 28. Типовой объём замера: 302 строк отчёта. Зависимость от базы: Строки отчёта - инструменты (Актив x Биржа), около 300 строк. Потоки: Один запрос, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. контроль котировок. отчет. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Загрузка котировок финальная за Т-1</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 36 дням. Замеров в выгрузке: 36. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов, от числа договоров не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: сумма этапов цикла, максимальный цикл за день, медиана по 40 дням. Замеров в выгрузке: 40. Типовой объём замера: 22 котировок. Зависимость от базы: Объём определяется числом инструментов, от числа договоров не зависит. Потоки: Один WS-вызов к Tibco, распараллеливание невозможно без изменения обмена. Окно: Цель IMDEV-8927: не дольше 30 минут. Ключевые операции регистра: Д у. загрузка котировок. получение tibco. фоновое выполнение; Д у. загрузка котировок. создание котировок. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Сверка с отчётом брокера</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 104 замерам. Замеров в выгрузке: 104. Типовой объём замера: 8052 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 8631 сделок -&gt; 112 с (n=75) и 18509 сделок -&gt; 310 с (n=2), то есть 0.0200 с на единицу плюс постоянные 0 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Окно сверки не менее 60 минут (старт 08:45). Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое выполнение.</t>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 116 замерам. Замеров в выгрузке: 116. Типовой объём замера: 7932 сделок. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 8441 сделок -&gt; 113 с (n=80) и 18509 сделок -&gt; 345 с (n=3), то есть 0.0231 с на единицу плюс постоянные 0 с. Зависимость от базы: Объём - число сделок за период (СделокИзSQL), растёт с базой клиентов. Потоки: Единый SQL плюс запросы 1С в одном процессе, пула потоков нет. Окно: Окно сверки не менее 60 минут (старт 08:45). Ключевые операции регистра: Д у. сверка. сделок с отчетом брокера. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Сверка остатков ЦБ с депозитарием</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 26 замерам. Замеров в выгрузке: 26. Типовой объём замера: 1 строк сверки. Зависимость от базы: Строки сверки - ДоговорДУ x ЦБ, сейчас около 121 000 строк. Потоки: Один SQL с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка ц б. сверка. фоновое выполнение.</t>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 28 замерам. Замеров в выгрузке: 28. Типовой объём замера: 1 строк сверки. Зависимость от базы: Строки сверки - ДоговорДУ x ЦБ, сейчас около 121 000 строк. Потоки: Один SQL с группировкой, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка ц б. сверка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Сверка API сигнал vs Реестры платежей</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 9 замерам. Замеров в выгрузке: 9. Типовой объём замера: 1 строк с минусом. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1 строк с минусом -&gt; 0 с (n=8) и 38 строк с минусом -&gt; 1 с (n=1), то есть 0.0077 с на единицу плюс постоянные 0 с. Зависимость от базы: Группировка АналитическийСчет + ДоговорДУ + Валюта по пулу Розничное ДУ. Потоки: Один запрос ОСВ, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка. отрицательные остатки на р с. формирование отчета. ручной.</t>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 12 замерам. Замеров в выгрузке: 12. Типовой объём замера: 1 строк с минусом. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 1 строк с минусом -&gt; 0 с (n=11) и 38 строк с минусом -&gt; 1 с (n=1), то есть 0.0082 с на единицу плюс постоянные 0 с. Зависимость от базы: Группировка АналитическийСчет + ДоговорДУ + Валюта по пулу Розничное ДУ. Потоки: Один запрос ОСВ, распараллеливание не предусмотрено. Окно: Окно сверки не менее 60 минут. Ключевые операции регистра: Д у. сверка. отрицательные остатки на р с. формирование отчета. ручной.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Процесс расторжения РДУ</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 3398 замерам. Замеров в выгрузке: 3398. Типовой объём замера: 137 договоров. Зависимость от базы: Вес замера - число договоров к расторжению из 1С:ДО. Потоки: Последовательная обработка договоров, пула потоков нет. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. расторжение договоров р д у. фоновое договоры из д о к расторжению.</t>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 3784 замерам. Замеров в выгрузке: 3784. Типовой объём замера: 136 договоров. Зависимость от базы: Вес замера - число договоров к расторжению из 1С:ДО. Потоки: Последовательная обработка договоров, пула потоков нет. Окно: Запуск каждые 10 минут по расписанию. Ключевые операции регистра: Д у. расторжение договоров р д у. фоновое договоры из д о к расторжению.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Загрузка договоров РДУ за дату Т, карточки клиента, автозаполнение аналитики для ВУ</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 3607 замерам; средний вес замера 1.23, прогноз от веса x10. Замеров в выгрузке: 3607. Типовой объём замера: 1 новых объектов НСИ. Модель роста: поток новинок: средний вес замера 1.23 новых объектов НСИ, 75.61 с на единицу; прогноз на средний вес x10 = 12.33. Зависимость от базы: Грузятся только новые договоры/карточки НСИ. Объём - средний вес замера (поток новинок); при росте базы в 10 раз средний поток новинок тоже вырастет примерно в 10 раз. Потоки: Последовательный обмен с 1С:ДО, распараллеливание не предусмотрено. Окно: Окно не более 30 минут (запуск каждые 10 минут по расписанию). Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение.</t>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 4014 замерам; средний вес замера 1.22, прогноз от веса x10. Замеров в выгрузке: 4014. Типовой объём замера: 1 новых объектов НСИ. Модель роста: поток новинок: средний вес замера 1.22 новых объектов НСИ, 74.87 с на единицу; прогноз на средний вес x10 = 12.16. Зависимость от базы: Грузятся только новые договоры/карточки НСИ. Объём - средний вес замера (поток новинок); при росте базы в 10 раз средний поток новинок тоже вырастет примерно в 10 раз. Потоки: Последовательный обмен с 1С:ДО, распараллеливание не предусмотрено. Окно: Окно не более 30 минут (запуск каждые 10 минут по расписанию). Ключевые операции регистра: Д у. синхронизация н с и. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Вечерние регламентные операции, расчёт РСА/СЧА за Т-1</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 3 замерам. Замеров в выгрузке: 3. Типовой объём замера: 21994 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3087 договоров -&gt; 1274 с (n=4) и 21994 договоров -&gt; 2542 с (n=3), то есть 0.0671 с на единицу плюс постоянные 1067 с. Зависимость от базы: Прямой перебор договоров РДУ: пачки по 3 000, чанки по 50 договоров на поток. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999, жёсткого предела в коде нет - резерв ограничен только ресурсами кластера. Окно: Окно не более 3 часов (180 минут). Ключевые операции регистра: Д у. регламентные операции.2. вечерние операции.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Утренние регламентные операции, начисления % по депозитам, РЕПО, НКД, погашения за дату Т</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 1 замерам; с ускорением x2.0 (IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.). Замеров в выгрузке: 1. Типовой объём замера: 22889 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3090 договоров -&gt; 437 с (n=27) и 22889 договоров -&gt; 3606 с (n=1), то есть 0.1601 с на единицу плюс постоянные 0 с учтено ускорение x2.0: IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.. Зависимость от базы: Прямой перебор договоров РДУ, тот же диспетчер пачек, что у вечерних. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999 - резерв ограничен ресурсами кластера. Окно: Окно не более 3 часов (180 минут). Ключевые операции регистра: Д у. регламентные операции.1. утренние операции.</t>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 1 замерам; с ускорением x2.0 (IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.). Замеров в выгрузке: 1. Типовой объём замера: 22889 договоров. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3090 договоров -&gt; 437 с (n=29) и 22889 договоров -&gt; 3606 с (n=1), то есть 0.1601 с на единицу плюс постоянные 0 с учтено ускорение x2.0: IMDEV-8863.1 (фоновые): вечерние ускорились примерно в 2 раза, утренние - тот же механизм, ожидается такое же ускорение.. Зависимость от базы: Прямой перебор договоров РДУ, тот же диспетчер пачек, что у вечерних. Потоки: Константа МаксимальноеКоличествоПараллельныхПотоков = 12. Резерв по потокам: Тип константы допускает до 999 - резерв ограничен ресурсами кластера. Окно: Окно не более 3 часов (180 минут). Ключевые операции регистра: Д у. регламентные операции.1. утренние операции.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Начисление вознаграждения</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Длительность: замер полного объёма: IMDEV-9153 DR 30.09.2026: параллельное начисление, пачки по 100, ~12 потоков; было последовательно 9 ч 52 мин 44 сек на 20 482 договоров. Замеров в выгрузке: 1. Типовой объём замера: 20467 договоров. Модель роста: удельная стоимость по замеру полного объёма: 20467 договоров -&gt; 3874 с (0.1893 с на договор). Зависимость от базы: Вес замера - число договоров к начислению. Потоки: Пул фоновых заданий, лимит из константы (12), пачки по 100 договоров зашиты в коде. Резерв по потокам: Лимит берётся из той же константы, что у регламентов - резерв ограничен ресурсами кластера. Окно: Квартальное закрытие, ночное окно. Ключевые операции регистра: Д у. начисление вознаграждения р д у. начисление. ручной; Д у. начисление вознаграждения р д у. начисление. начисление вознаграждения при расторжении розничное д у фоновое.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Оплата вознаграждения</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: замер в код не вставлен. Зависимость от базы: Отбор договоров РДУ, объём прямо пропорционален базе. Потоки: Последовательный перебор строк ДокументыКВыгрузке, пула потоков нет. Окно: Квартальное закрытие, ночное окно.</t>
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Оплата вознаграждения (Оплата КЗ)</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 9213 договоров. Зависимость от базы: Отбор договоров РДУ. Полный замер: блокировка ДС, 9 213 договоров. Поручения/поступление/списание пока только на 7 договорах. Потоки: Последовательный перебор строк ДокументыКВыгрузке, пула потоков нет. Окно: Квартальное закрытие, ночное окно. Ключевые операции регистра: Д у. оплата к з р д у. блокировка д с; Д у. оплата к з р д у. поручения в мидл; Д у. оплата к з р д у. поступление на расчетный счет; Д у. оплата к з р д у. списание с расчетного счета.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Массовое построение Отчётов РДУ и выгрузка в КК</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: среднее за день: 4.7 мин, среднее к-во договоров/день: 20; полный квартальный прогон в выгрузке отсутствует - прогноз не публикуется. Замеров в выгрузке: 27. Типовой объём замера: 20 договоров/день. Зависимость от базы: Регламент обрабатывает очередь регистра СостоянияВыгрузкиОтчетовДУ. Очередь пополняется, когда пуста: квартально - всем пулом "Розничное ДУ", плюс ежедневно договорами с датой окончания. То есть квартальный прогон - это один отчёт на каждый договор РДУ. Потоки: Реквизит Отчет.КоличествоПотоков. В обработчиках формы стоит жёсткая отсечка: если больше 10, значение сбрасывается в 10. Многопоточность работает только в режиме "по клиентам розничного ДУ в фоновых потоках" (РежимРаботы=2) - именно он используется регламентом. Окно: Ночное окно 8 часов после старта 17:00. Ключевые операции регистра: Отчет управляющего д у 482 п.</t>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: среднее за день: 4.8 мин, среднее к-во договоров/день: 21; полный квартальный прогон в выгрузке отсутствует - прогноз не публикуется. Замеров в выгрузке: 29. Типовой объём замера: 21 договоров/день. Зависимость от базы: Регламент обрабатывает очередь регистра СостоянияВыгрузкиОтчетовДУ. Очередь пополняется, когда пуста: квартально - всем пулом "Розничное ДУ", плюс ежедневно договорами с датой окончания. То есть квартальный прогон - это один отчёт на каждый договор РДУ. Потоки: Реквизит Отчет.КоличествоПотоков. В обработчиках формы стоит жёсткая отсечка: если больше 10, значение сбрасывается в 10. Многопоточность работает только в режиме "по клиентам розничного ДУ в фоновых потоках" (РежимРаботы=2) - именно он используется регламентом. Окно: Ночное окно 8 часов после старта 17:00. Ключевые операции регистра: Отчет управляющего д у 482 п.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Выгрузка данных в кабинет клиента ДУ (экспорт HNWI)</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 2944 замерам. Замеров в выгрузке: 2944. Типовой объём замера: 1 клиентов и дат. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3 клиентов и дат -&gt; 8 с (n=149) и 5 клиентов и дат -&gt; 10 с (n=386), то есть 0.7648 с на единицу плюс постоянные 6 с. Зависимость от базы: Вес замера - клиенты и даты инвестирования. Потоки: Последовательная выгрузка, ограничение на стороне принимающей системы (кабинет). Окно: Инкрементальный запуск каждые 10 минут. Ключевые операции регистра: Д у. экспорт h n w i. выгрузка. фоновое выполнение.</t>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 3278 замерам. Замеров в выгрузке: 3278. Типовой объём замера: 1 клиентов и дат. Модель роста: предельная стоимость единицы объёма по двум верхним уровням: 3 клиентов и дат -&gt; 8 с (n=156) и 5 клиентов и дат -&gt; 10 с (n=405), то есть 0.8095 с на единицу плюс постоянные 6 с. Зависимость от базы: Вес замера - клиенты и даты инвестирования. Потоки: Последовательная выгрузка, ограничение на стороне принимающей системы (кабинет). Окно: Инкрементальный запуск каждые 10 минут. Ключевые операции регистра: Д у. экспорт h n w i. выгрузка. фоновое выполнение.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Распределение доходов по ценным бумагам</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Длительность: медиана по 1 замерам. Замеров в выгрузке: 1. Типовой объём замера: 13361 строк НКД. Зависимость от базы: Объём - отмеченные строки НКД/погашений/дивидендов по позициям договоров. Потоки: Лимит из константы МаксимальноеКоличествоПараллельныхПотоков (12), пачки по 100 строк. Резерв по потокам: Резерв ограничен ресурсами кластера. Окно: Ночное окно 8 часов. Ключевые операции регистра: Д у. распределение доходов. создание операций.вн распределение доходов по ценным бумагам.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Расчёт вознаграждения РДУ (ожидаемые платежи)</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>Длительность: медиана по 36 замерам. Замеров в выгрузке: 36. Типовой объём замера: 1 договоров к расчёту. Зависимость от базы: Отбор договоров пула Розничное ДУ. Потоки: Последовательный перебор ДоговорыДУКРасчету. Окно: Старт 08:00, до начала операционного дня. Ключевые операции регистра: Д у. расчет вознаграждения р д у. расчет. фоновое выполнение.</t>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Длительность: медиана по 40 замерам. Замеров в выгрузке: 40. Типовой объём замера: 1 договоров к расчёту. Зависимость от базы: Отбор договоров пула Розничное ДУ. Потоки: Последовательный перебор ДоговорыДУКРасчету. Окно: Старт 08:00, до начала операционного дня. Ключевые операции регистра: Д у. расчет вознаграждения р д у. расчет. фоновое выполнение.</t>
         </is>
       </c>
     </row>
@@ -2805,188 +2779,188 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Подсветка строки</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr"/>
+      <c r="B1" s="26" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Красный</t>
         </is>
       </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Предел ниже целевых 250 тыс. договоров - операция не выдержит рост базы.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Жёлтый</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Предел от 250 до 500 тыс. договоров - запас менее двукратного.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Зелёный</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Запас достаточный либо операция не зависит от числа клиентов.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Оранжевый</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Нет квартальной выгрузки массового прогона: показано среднее за день и среднее число договоров/день; прогноз и предел не публикуются.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Серый</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Замер в код не вставлен: длительность и прогноз не рассчитываются (прочерк).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr"/>
-      <c r="B7" s="31" t="inlineStr"/>
+      <c r="A7" s="30" t="inlineStr"/>
+      <c r="B7" s="26" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr"/>
+      <c r="B8" s="26" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Длительность сейчас</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Медиана прогонов на полном объёме базы: только регламентный контур, вес замера от 15 тыс. договоров, аварийные замеры исключены.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Длительность макс</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Максимум длительности среди тех же отобранных замеров (полный объём, без аварийных).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Время запуска</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>По фактическим замерам: первое типичное время старта за день, частота запусков, последнее типичное время старта. Формат: ЧЧ:ММ, N мин (или 1 раз), ЧЧ:ММ.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Прогноз x10 линейный</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Текущая длительность, умноженная на 10. Для загрузки/исполнения сделок применяется по допущению: интенсивность сделок на договор постоянна. Не применяется к операциям, не зависящим от числа договоров (котировки, счета ЕРС).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Прогноз расчётный</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Линейная модель ПостояннаяЧасть + СтоимостьЕдиницы * Объём. Наклон по двум самым крупным уровням объёма из фактических замеров.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Потоков макс</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Только предел, подтверждённый кодом: жёсткое значение, ограничение интерфейса или значение константы. Где предел упирается в ресурсы кластера, а не в код, максимум приравнен к текущему значению, а резерв описан на листе "Методика и детали".</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Предел, тыс. договоров</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Число договоров, при котором операция упирается в своё окно выполнения. Для сделок - через пересчёт объёма сделок при постоянной интенсивности на договор (окно исполнения: 2 ч на 200 тыс. сделок).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Пометка "оценка"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Массового прогона в выгрузке нет, цифра получена пересчётом от удельной стоимости договора. Требуется замер массового прогона.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Пометка "нет замеров"</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Замер в код не вставлен. Расчёт по аналогии не делается - в ячейках прочерк.</t>
         </is>
